--- a/PreC2D/Relation_CN_Str_Formation.xlsx
+++ b/PreC2D/Relation_CN_Str_Formation.xlsx
@@ -1,26 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R-4.4.1\Cerema_formation\PreC2D\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C106C-B318-4DAC-89F8-8852B7F16F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Liens" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="BDTopo" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Cn_Stockage" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Explications_Colonnes" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Feuil1" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="CLC_IA_Mistral" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="RPG" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Liens" sheetId="1" r:id="rId1"/>
+    <sheet name="BDTopo" sheetId="2" r:id="rId2"/>
+    <sheet name="Cn_Stockage" sheetId="3" r:id="rId3"/>
+    <sheet name="Explications_Colonnes" sheetId="4" r:id="rId4"/>
+    <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
+    <sheet name="CLC_IA_Mistral" sheetId="6" r:id="rId6"/>
+    <sheet name="RPG" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liens!$A$1:$V$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">RPG!$A$2:$C$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liens!$A$1:$V$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">RPG!$A$2:$C$26</definedName>
   </definedNames>
-  <calcPr iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,16 +47,16 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={00DA0082-008E-47F5-9D71-00DC005700B4}</author>
+    <author>tc={003F0060-0036-4297-BF72-00D700BD000C}</author>
     <author>tc={001D0026-0028-41E0-ADB6-006A005400ED}</author>
     <author>tc={00A80029-00B3-483C-875A-0039008D0013}</author>
     <author>tc={007F0009-00DB-4CFA-BF3A-00D500530037}</author>
     <author>tc={005A0009-005F-45B1-93A4-005000CB00CB}</author>
     <author>tc={002500B0-0092-4618-A8DA-00BD006E0028}</author>
     <author>tc={00800048-00DB-4A8F-9590-00B600890008}</author>
-    <author>tc={003F0060-0036-4297-BF72-00D700BD000C}</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" xr:uid="{00DA0082-008E-47F5-9D71-00DC005700B4}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00DA0082-008E-47F5-9D71-00DC005700B4}">
       <text>
         <r>
           <rPr>
@@ -45,7 +64,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -61,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="1" xr:uid="{001D0026-0028-41E0-ADB6-006A005400ED}">
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{003F0060-0036-4297-BF72-00D700BD000C}">
       <text>
         <r>
           <rPr>
@@ -69,7 +88,31 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
+    Chemin de la couche ou identifiant
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{001D0026-0028-41E0-ADB6-006A005400ED}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -85,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="2" xr:uid="{00A80029-00B3-483C-875A-0039008D0013}">
+    <comment ref="L1" authorId="3" shapeId="0" xr:uid="{00A80029-00B3-483C-875A-0039008D0013}">
       <text>
         <r>
           <rPr>
@@ -93,7 +136,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -109,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="3" xr:uid="{007F0009-00DB-4CFA-BF3A-00D500530037}">
+    <comment ref="N1" authorId="4" shapeId="0" xr:uid="{007F0009-00DB-4CFA-BF3A-00D500530037}">
       <text>
         <r>
           <rPr>
@@ -117,7 +160,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -133,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="4" xr:uid="{005A0009-005F-45B1-93A4-005000CB00CB}">
+    <comment ref="O1" authorId="5" shapeId="0" xr:uid="{005A0009-005F-45B1-93A4-005000CB00CB}">
       <text>
         <r>
           <rPr>
@@ -141,7 +184,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -157,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="5" xr:uid="{002500B0-0092-4618-A8DA-00BD006E0028}">
+    <comment ref="P1" authorId="6" shapeId="0" xr:uid="{002500B0-0092-4618-A8DA-00BD006E0028}">
       <text>
         <r>
           <rPr>
@@ -165,7 +208,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -181,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="6" xr:uid="{00800048-00DB-4A8F-9590-00B600890008}">
+    <comment ref="R1" authorId="7" shapeId="0" xr:uid="{00800048-00DB-4A8F-9590-00B600890008}">
       <text>
         <r>
           <rPr>
@@ -189,7 +232,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -205,7 +248,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="7" xr:uid="{003F0060-0036-4297-BF72-00D700BD000C}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={00EB004B-00B1-4B56-879E-004100800038}</author>
+    <author>tc={00B4009B-0065-4BB8-A466-00CE00B70075}</author>
+    <author>tc={00CA00A1-00FB-4062-82F2-001700BE00E8}</author>
+    <author>tc={003F009F-00F0-4A15-8727-0018009B0072}</author>
+    <author>tc={00AC00B7-00A9-46C1-9B91-000500AA0006}</author>
+    <author>tc={00D60031-0029-466D-8357-00B5009E0025}</author>
+    <author>tc={00140070-00CD-45CD-8A69-0058003E0061}</author>
+    <author>tc={00F4001A-008A-43BD-86A5-002300A20033}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00EB004B-00B1-4B56-879E-004100800038}">
       <text>
         <r>
           <rPr>
@@ -213,7 +273,31 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
+    Mettre l'ordre du Strickler
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="1" shapeId="0" xr:uid="{00B4009B-0065-4BB8-A466-00CE00B70075}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -229,24 +313,7 @@
         </r>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={00EB004B-00B1-4B56-879E-004100800038}</author>
-    <author>tc={003F009F-00F0-4A15-8727-0018009B0072}</author>
-    <author>tc={00AC00B7-00A9-46C1-9B91-000500AA0006}</author>
-    <author>tc={00D60031-0029-466D-8357-00B5009E0025}</author>
-    <author>tc={00140070-00CD-45CD-8A69-0058003E0061}</author>
-    <author>tc={00F4001A-008A-43BD-86A5-002300A20033}</author>
-    <author>tc={00B4009B-0065-4BB8-A466-00CE00B70075}</author>
-    <author>tc={00CA00A1-00FB-4062-82F2-001700BE00E8}</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" xr:uid="{00EB004B-00B1-4B56-879E-004100800038}">
+    <comment ref="A10" authorId="2" shapeId="0" xr:uid="{00CA00A1-00FB-4062-82F2-001700BE00E8}">
       <text>
         <r>
           <rPr>
@@ -254,7 +321,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -265,12 +332,12 @@
 [Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
-    Mettre l'ordre du Strickler
+    Nom du fichier
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="1" xr:uid="{003F009F-00F0-4A15-8727-0018009B0072}">
+    <comment ref="A11" authorId="3" shapeId="0" xr:uid="{003F009F-00F0-4A15-8727-0018009B0072}">
       <text>
         <r>
           <rPr>
@@ -278,7 +345,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -294,7 +361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="2" xr:uid="{00AC00B7-00A9-46C1-9B91-000500AA0006}">
+    <comment ref="A12" authorId="4" shapeId="0" xr:uid="{00AC00B7-00A9-46C1-9B91-000500AA0006}">
       <text>
         <r>
           <rPr>
@@ -302,7 +369,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -318,7 +385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="3" xr:uid="{00D60031-0029-466D-8357-00B5009E0025}">
+    <comment ref="A13" authorId="5" shapeId="0" xr:uid="{00D60031-0029-466D-8357-00B5009E0025}">
       <text>
         <r>
           <rPr>
@@ -326,7 +393,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -342,7 +409,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A14" authorId="4" xr:uid="{00140070-00CD-45CD-8A69-0058003E0061}">
+    <comment ref="A14" authorId="6" shapeId="0" xr:uid="{00140070-00CD-45CD-8A69-0058003E0061}">
       <text>
         <r>
           <rPr>
@@ -350,7 +417,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -366,7 +433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A15" authorId="5" xr:uid="{00F4001A-008A-43BD-86A5-002300A20033}">
+    <comment ref="A15" authorId="7" shapeId="0" xr:uid="{00F4001A-008A-43BD-86A5-002300A20033}">
       <text>
         <r>
           <rPr>
@@ -374,7 +441,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
+          <t>Auteur inconnu:</t>
         </r>
         <r>
           <rPr>
@@ -390,60 +457,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="6" xr:uid="{00B4009B-0065-4BB8-A466-00CE00B70075}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Chemin de la couche ou identifiant
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A10" authorId="7" xr:uid="{00CA00A1-00FB-4062-82F2-001700BE00E8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Auteur inconnu:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Nom du fichier
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="218">
   <si>
     <t>ID</t>
   </si>
@@ -508,10 +527,10 @@
     <t>Type_geometrie</t>
   </si>
   <si>
-    <t xml:space="preserve">Valeur Strickler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choix subjectif</t>
+    <t>Valeur Strickler</t>
+  </si>
+  <si>
+    <t>choix subjectif</t>
   </si>
   <si>
     <t>BDTopo</t>
@@ -526,7 +545,7 @@
     <t>Polygone</t>
   </si>
   <si>
-    <t xml:space="preserve">Urban Areas - Roofs</t>
+    <t>Urban Areas - Roofs</t>
   </si>
   <si>
     <t>batiment</t>
@@ -543,11 +562,11 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">LIKE '%Serre%'</t>
+      <t>LIKE '%Serre%'</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Urban Areas - Driveways</t>
+    <t>Urban Areas - Driveways</t>
   </si>
   <si>
     <t>piste_d_aerodrome</t>
@@ -559,25 +578,25 @@
     <t>largeur_de_chaussee</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt; 5</t>
+    <t>&gt; 5</t>
   </si>
   <si>
     <t>Ligne</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt; 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS NULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban areas - Gravels</t>
+    <t>&gt; 3</t>
+  </si>
+  <si>
+    <t>&gt; 2</t>
+  </si>
+  <si>
+    <t>&gt;= 0</t>
+  </si>
+  <si>
+    <t>IS NULL</t>
+  </si>
+  <si>
+    <t>Urban areas - Gravels</t>
   </si>
   <si>
     <t>troncon_de_voie_ferree</t>
@@ -594,23 +613,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">LIKE '%Etroite%'</t>
+      <t>LIKE '%Etroite%'</t>
     </r>
   </si>
   <si>
     <t>Normale</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Normale%'</t>
+    <t>LIKE '%Normale%'</t>
   </si>
   <si>
     <t>Large</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Large%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban areas - Paved</t>
+    <t>LIKE '%Large%'</t>
+  </si>
+  <si>
+    <t>Urban areas - Paved</t>
   </si>
   <si>
     <t>equipement_de_transport</t>
@@ -624,17 +643,17 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">LIKE '%Parking%'</t>
+      <t>LIKE '%Parking%'</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Urban areas - Cemeteries</t>
+    <t>Urban areas - Cemeteries</t>
   </si>
   <si>
     <t>cimetiere</t>
   </si>
   <si>
-    <t xml:space="preserve">Agriculture lands - Woods - Fair</t>
+    <t>Agriculture lands - Woods - Fair</t>
   </si>
   <si>
     <t>zone_de_vegetation</t>
@@ -643,223 +662,82 @@
     <t>Bois</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Bois%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture lands - Woods - Good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forêt fermée de conifères</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%e de conif%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forêt fermée de feuillus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%e de feuillus%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forêt fermée mixte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%e mixte%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture lands - Woods - poor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forêt ouverte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%t ouverte%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture lands - Brush - poor</t>
+    <t>LIKE '%Bois%'</t>
+  </si>
+  <si>
+    <t>Agriculture lands - Woods - Good</t>
+  </si>
+  <si>
+    <t>Forêt fermée de conifères</t>
+  </si>
+  <si>
+    <t>LIKE '%e de conif%'</t>
+  </si>
+  <si>
+    <t>Forêt fermée de feuillus</t>
+  </si>
+  <si>
+    <t>LIKE '%e de feuillus%'</t>
+  </si>
+  <si>
+    <t>Forêt fermée mixte</t>
+  </si>
+  <si>
+    <t>LIKE '%e mixte%'</t>
+  </si>
+  <si>
+    <t>Agriculture lands - Woods - poor</t>
+  </si>
+  <si>
+    <t>Forêt ouverte</t>
+  </si>
+  <si>
+    <t>LIKE '%t ouverte%'</t>
+  </si>
+  <si>
+    <t>Agriculture lands - Brush - poor</t>
   </si>
   <si>
     <t>Haie</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Haie%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lande ligneuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%Lande ligneuse%'</t>
+    <t>LIKE '%Haie%'</t>
+  </si>
+  <si>
+    <t>Lande ligneuse</t>
+  </si>
+  <si>
+    <t>LIKE '%Lande ligneuse%'</t>
   </si>
   <si>
     <t>Peupleraie</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Peupleraie%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture lands - Woods-Gras combinaison - Fair</t>
+    <t>LIKE '%Peupleraie%'</t>
+  </si>
+  <si>
+    <t>Agriculture lands - Woods-Gras combinaison - Fair</t>
   </si>
   <si>
     <t>Verger</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Verger%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture lands - Woods-Gras combinaison - Poor</t>
+    <t>LIKE '%Verger%'</t>
+  </si>
+  <si>
+    <t>Agriculture lands - Woods-Gras combinaison - Poor</t>
   </si>
   <si>
     <t>Vigne</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%Vigne%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IA Mistral</t>
-  </si>
-  <si>
-    <t>G:\u2018_clc2018_v2020_20u1_geoPackage\DATA</t>
-  </si>
-  <si>
-    <t>U2018_CLC2018_V2020_20u1_EPSG2154_Formation.gpkg</t>
+    <t>LIKE '%Vigne%'</t>
   </si>
   <si>
     <t>Code_18</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKE '%111%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%112%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%121%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%122%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%123%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%124%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%131%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%132%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%133%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%141%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%142%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%211%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%212%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%213%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%221%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%222%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%223%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%231%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%241%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%242%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%243%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%244%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%311%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%312%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%313%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%321%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%322%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%323%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%324%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%331%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%332%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%333%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%334%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%335%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%411%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%412%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%421%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%422%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%423%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%511%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%512%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%521%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%522%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKE '%523%'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve Number_A</t>
+    <t>Curve Number_A</t>
   </si>
   <si>
     <t>Batiments</t>
@@ -871,34 +749,34 @@
     <t>IGN</t>
   </si>
   <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 troncon_de_route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 piste_d_aerodrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voies ferrées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 troncon_de_voie_ferree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface hydrographique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 surface_hydrographique</t>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 troncon_de_route</t>
+  </si>
+  <si>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 piste_d_aerodrome</t>
+  </si>
+  <si>
+    <t>Voies ferrées</t>
+  </si>
+  <si>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 troncon_de_voie_ferree</t>
+  </si>
+  <si>
+    <t>Surface hydrographique</t>
+  </si>
+  <si>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 surface_hydrographique</t>
   </si>
   <si>
     <t>Forêt</t>
   </si>
   <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 foret_publique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone de végétation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 zone_de_vegetation</t>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 foret_publique</t>
+  </si>
+  <si>
+    <t>Zone de végétation</t>
+  </si>
+  <si>
+    <t>BDT_3-0_GPKG_LAMB93_D034-ED2021-09-15 zone_de_vegetation</t>
   </si>
   <si>
     <t>Cimétière</t>
@@ -907,7 +785,7 @@
     <t>Agriculture</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone d'activités</t>
+    <t>Zone d'activités</t>
   </si>
   <si>
     <t>Canaux</t>
@@ -925,49 +803,49 @@
     <t>Identifiant</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordre de priorité Strickler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeur du Strickler (si nul, valeur lue dans le fichier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeur du CN (si nul, valeur lue dans le fichier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemin de la données ou code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom du fichier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom de la couche dans le fichier (pour format GPKG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champ à analyser (si nécessaire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeur du Champ compatible R à analyser (si nécessaire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeur du Champ à analyser (si nécessaire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nom du champ pour les tampons (sur des objets linéaires)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test de superficies de zones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vecteur ou raster (non codé pour l'instant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lignes, polygones…</t>
+    <t>Ordre de priorité Strickler</t>
+  </si>
+  <si>
+    <t>Valeur du Strickler (si nul, valeur lue dans le fichier)</t>
+  </si>
+  <si>
+    <t>Valeur du CN (si nul, valeur lue dans le fichier)</t>
+  </si>
+  <si>
+    <t>Chemin de la données ou code</t>
+  </si>
+  <si>
+    <t>Nom du fichier</t>
+  </si>
+  <si>
+    <t>Nom de la couche dans le fichier (pour format GPKG)</t>
+  </si>
+  <si>
+    <t>Champ à analyser (si nécessaire)</t>
+  </si>
+  <si>
+    <t>Valeur du Champ compatible R à analyser (si nécessaire)</t>
+  </si>
+  <si>
+    <t>Valeur du Champ à analyser (si nécessaire)</t>
+  </si>
+  <si>
+    <t>nom du champ pour les tampons (sur des objets linéaires)</t>
+  </si>
+  <si>
+    <t>Test de superficies de zones</t>
+  </si>
+  <si>
+    <t>vecteur ou raster (non codé pour l'instant)</t>
+  </si>
+  <si>
+    <t>lignes, polygones…</t>
   </si>
   <si>
     <t>Liens</t>
   </si>
   <si>
-    <t xml:space="preserve">United States
+    <t>United States
 Department of Agriculture
 Natural Resources Conservation Service Conservation
 Engineering Division Technical
@@ -977,16 +855,16 @@
 TR-55</t>
   </si>
   <si>
-    <t xml:space="preserve">Voir comment enlever les serres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Batiments sur une route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">voir comment gérer - Obligation pour PPRi Montpellier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Batiments sur une voie ferrée</t>
+    <t>Voir comment enlever les serres</t>
+  </si>
+  <si>
+    <t>Batiments sur une route</t>
+  </si>
+  <si>
+    <t>voir comment gérer - Obligation pour PPRi Montpellier</t>
+  </si>
+  <si>
+    <t>Batiments sur une voie ferrée</t>
   </si>
   <si>
     <t>RPG</t>
@@ -995,163 +873,163 @@
     <t>https://geoservices.ign.fr/rpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Le registre parcellaire graphique est une base de données géographiques servant de référence à l'instruction des aides de la politique agricole commune (PAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORINE Land Cover Class</t>
+    <t>Le registre parcellaire graphique est une base de données géographiques servant de référence à l'instruction des aides de la politique agricole commune (PAC)</t>
+  </si>
+  <si>
+    <t>CORINE Land Cover Class</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Curve Number (A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve Number (B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve Number (C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve Number (D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continuous urban fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discontinuous urban fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial or commercial units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Road and rail networks and associated land</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port areas</t>
+    <t>Curve Number (A)</t>
+  </si>
+  <si>
+    <t>Curve Number (B)</t>
+  </si>
+  <si>
+    <t>Curve Number (C)</t>
+  </si>
+  <si>
+    <t>Curve Number (D)</t>
+  </si>
+  <si>
+    <t>Continuous urban fabric</t>
+  </si>
+  <si>
+    <t>Discontinuous urban fabric</t>
+  </si>
+  <si>
+    <t>Industrial or commercial units</t>
+  </si>
+  <si>
+    <t>Road and rail networks and associated land</t>
+  </si>
+  <si>
+    <t>Port areas</t>
   </si>
   <si>
     <t>Airports</t>
   </si>
   <si>
-    <t xml:space="preserve">Mineral extraction sites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dump sites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction sites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green urban areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sport and leisure facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-irrigated arable land</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permanently irrigated land</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rice fields</t>
+    <t>Mineral extraction sites</t>
+  </si>
+  <si>
+    <t>Dump sites</t>
+  </si>
+  <si>
+    <t>Construction sites</t>
+  </si>
+  <si>
+    <t>Green urban areas</t>
+  </si>
+  <si>
+    <t>Sport and leisure facilities</t>
+  </si>
+  <si>
+    <t>Non-irrigated arable land</t>
+  </si>
+  <si>
+    <t>Permanently irrigated land</t>
+  </si>
+  <si>
+    <t>Rice fields</t>
   </si>
   <si>
     <t>Vineyards</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruit trees and berry plantations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olive groves</t>
+    <t>Fruit trees and berry plantations</t>
+  </si>
+  <si>
+    <t>Olive groves</t>
   </si>
   <si>
     <t>Pastures</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual crops associated with permanent crops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complex cultivation patterns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land principally occupied by agriculture, with significant areas of natural vegetation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agro-forestry areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broad-leaved forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coniferous forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural grasslands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moors and heathland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sclerophyllous vegetation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transitional woodland-shrub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beaches, dunes, sands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare rocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sparsely vegetated areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burnt areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glaciers and perpetual snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inland marshes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peat bogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt marshes</t>
+    <t>Annual crops associated with permanent crops</t>
+  </si>
+  <si>
+    <t>Complex cultivation patterns</t>
+  </si>
+  <si>
+    <t>Land principally occupied by agriculture, with significant areas of natural vegetation</t>
+  </si>
+  <si>
+    <t>Agro-forestry areas</t>
+  </si>
+  <si>
+    <t>Broad-leaved forest</t>
+  </si>
+  <si>
+    <t>Coniferous forest</t>
+  </si>
+  <si>
+    <t>Mixed forest</t>
+  </si>
+  <si>
+    <t>Natural grasslands</t>
+  </si>
+  <si>
+    <t>Moors and heathland</t>
+  </si>
+  <si>
+    <t>Sclerophyllous vegetation</t>
+  </si>
+  <si>
+    <t>Transitional woodland-shrub</t>
+  </si>
+  <si>
+    <t>Beaches, dunes, sands</t>
+  </si>
+  <si>
+    <t>Bare rocks</t>
+  </si>
+  <si>
+    <t>Sparsely vegetated areas</t>
+  </si>
+  <si>
+    <t>Burnt areas</t>
+  </si>
+  <si>
+    <t>Glaciers and perpetual snow</t>
+  </si>
+  <si>
+    <t>Inland marshes</t>
+  </si>
+  <si>
+    <t>Peat bogs</t>
+  </si>
+  <si>
+    <t>Salt marshes</t>
   </si>
   <si>
     <t>Salines</t>
   </si>
   <si>
-    <t xml:space="preserve">Intertidal flats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water courses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water bodies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coastal lagoons</t>
+    <t>Intertidal flats</t>
+  </si>
+  <si>
+    <t>Water courses</t>
+  </si>
+  <si>
+    <t>Water bodies</t>
+  </si>
+  <si>
+    <t>Coastal lagoons</t>
   </si>
   <si>
     <t>Estuaries</t>
   </si>
   <si>
-    <t xml:space="preserve">Sea and ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mistral manuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mistral automatique</t>
+    <t>Sea and ocean</t>
+  </si>
+  <si>
+    <t>Mistral manuel</t>
+  </si>
+  <si>
+    <t>Mistral automatique</t>
   </si>
   <si>
     <t>CODE_GROUPE_CULTURE</t>
@@ -1160,34 +1038,34 @@
     <t>LIBELLE_GROUPE_CULTURE</t>
   </si>
   <si>
-    <t xml:space="preserve">Sol A (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sol B (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sol C (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sol D (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groupe de Sol (RPG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blé tendre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve Number (CN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maïs grain et ensilage</t>
+    <t>Sol A (CN)</t>
+  </si>
+  <si>
+    <t>Sol B (CN)</t>
+  </si>
+  <si>
+    <t>Sol C (CN)</t>
+  </si>
+  <si>
+    <t>Sol D (CN)</t>
+  </si>
+  <si>
+    <t>Groupe de Sol (RPG)</t>
+  </si>
+  <si>
+    <t>Blé tendre</t>
+  </si>
+  <si>
+    <t>Curve Number (CN)</t>
+  </si>
+  <si>
+    <t>Maïs grain et ensilage</t>
   </si>
   <si>
     <t>Orge</t>
   </si>
   <si>
-    <t xml:space="preserve">Autres céréales</t>
+    <t>Autres céréales</t>
   </si>
   <si>
     <t>Colza</t>
@@ -1196,34 +1074,34 @@
     <t>Tournesol</t>
   </si>
   <si>
-    <t xml:space="preserve">Autres oléagineux</t>
+    <t>Autres oléagineux</t>
   </si>
   <si>
     <t>Protéagineux</t>
   </si>
   <si>
-    <t xml:space="preserve">Plantes à fibres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gel (surfaces gelées sans production)</t>
+    <t>Plantes à fibres</t>
+  </si>
+  <si>
+    <t>Gel (surfaces gelées sans production)</t>
   </si>
   <si>
     <t>Riz</t>
   </si>
   <si>
-    <t xml:space="preserve">Légumineuses à grains</t>
+    <t>Légumineuses à grains</t>
   </si>
   <si>
     <t>Fourrage</t>
   </si>
   <si>
-    <t xml:space="preserve">Estives et landes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prairies permanentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prairies temporaires</t>
+    <t>Estives et landes</t>
+  </si>
+  <si>
+    <t>Prairies permanentes</t>
+  </si>
+  <si>
+    <t>Prairies temporaires</t>
   </si>
   <si>
     <t>Vergers</t>
@@ -1232,67 +1110,95 @@
     <t>Vignes</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruits à coque</t>
+    <t>Fruits à coque</t>
   </si>
   <si>
     <t>Oliviers</t>
   </si>
   <si>
-    <t xml:space="preserve">Autres cultures industrielles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Légumes ou fleurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canne à sucre</t>
+    <t>Autres cultures industrielles</t>
+  </si>
+  <si>
+    <t>Légumes ou fleurs</t>
+  </si>
+  <si>
+    <t>Canne à sucre</t>
   </si>
   <si>
     <t>Divers</t>
+  </si>
+  <si>
+    <t>IA Mistral + manuel</t>
+  </si>
+  <si>
+    <t>LIKE '1'</t>
+  </si>
+  <si>
+    <t>C:\BDD\RPG_3-0__GPKG_LAMB93_R93_2024-01-01\RPG\1_DONNEES_LIVRAISON_2024\RPG_3-0__GPKG_LAMB93_R93_2024-01-01</t>
+  </si>
+  <si>
+    <t>RPG_Parcelles.gpkg</t>
+  </si>
+  <si>
+    <t>code_group</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.000000"/>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="8.000000"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1341,11 +1247,11 @@
   </fills>
   <borders count="3">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1360,7 +1266,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1369,98 +1275,110 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" vertical="top"/>
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="2" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="4" borderId="1" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1468,13 +1386,16 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1487,9 +1408,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="ZoneTexte 1"/>
+        <xdr:cNvPr id="2" name="ZoneTexte 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1523,7 +1450,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1536,9 +1463,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="3" name="ZoneTexte 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1560,6 +1493,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1570,7 +1504,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1583,9 +1517,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="4" name="ZoneTexte 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1607,6 +1547,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1617,7 +1558,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1630,9 +1571,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="5" name="ZoneTexte 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1654,6 +1601,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1664,7 +1612,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1677,9 +1625,15 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="6" name="ZoneTexte 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1701,6 +1655,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1711,7 +1666,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1724,9 +1679,15 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="7" name="ZoneTexte 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1748,6 +1709,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1758,7 +1720,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1771,9 +1733,15 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="8" name="ZoneTexte 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1795,6 +1763,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1805,7 +1774,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1818,9 +1787,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="9" name="ZoneTexte 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1842,6 +1817,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1852,7 +1828,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
@@ -1865,9 +1841,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="10" name="ZoneTexte 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
@@ -1889,6 +1871,7 @@
       </xdr:spPr>
       <xdr:txBody>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr/>
@@ -1908,291 +1891,8 @@
 </personList>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -2244,7 +1944,7 @@
         <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2313,6 +2013,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -2439,31 +2140,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AH46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="8" style="1" width="4.28515625"/>
-    <col customWidth="1" min="9" max="9" style="2" width="35.140625"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" style="1" width="46"/>
-    <col customWidth="1" min="11" max="11" style="1" width="43.7109375"/>
-    <col customWidth="1" min="12" max="13" style="1" width="25.5703125"/>
-    <col bestFit="1" customWidth="1" min="14" max="14" style="1" width="23.140625"/>
-    <col customWidth="1" min="15" max="15" style="1" width="45.85546875"/>
-    <col customWidth="1" min="16" max="16" style="1" width="35.140625"/>
-    <col customWidth="1" min="17" max="17" style="2" width="3.5703125"/>
-    <col customWidth="1" min="18" max="18" style="1" width="21"/>
-    <col customWidth="1" min="19" max="19" style="2" width="5.7109375"/>
-    <col customWidth="1" min="20" max="20" style="1" width="8"/>
-    <col customWidth="1" min="21" max="21" style="1" width="9.42578125"/>
-    <col customWidth="1" min="22" max="22" style="1" width="58.85546875"/>
-    <col min="23" max="16384" style="1" width="10.7109375"/>
+    <col min="1" max="8" width="4.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="46" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.6640625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="25.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="35.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.5546875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="21" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.44140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="58.88671875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94.5">
+    <row r="1" spans="1:34" ht="96" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2531,10 +2232,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9">
+        <v>30</v>
+      </c>
       <c r="D2" s="9">
         <v>1</v>
       </c>
@@ -2575,9 +2280,11 @@
       </c>
       <c r="V2" s="9"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
+      <c r="B3" s="9">
+        <v>2</v>
+      </c>
       <c r="C3" s="9">
         <v>10</v>
       </c>
@@ -2627,9 +2334,11 @@
       </c>
       <c r="V3" s="9"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
+      <c r="B4" s="9">
+        <v>3</v>
+      </c>
       <c r="C4" s="9">
         <v>5</v>
       </c>
@@ -2673,10 +2382,14 @@
       </c>
       <c r="V4" s="9"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="B5" s="9">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9">
+        <v>30</v>
+      </c>
       <c r="D5" s="9">
         <v>4</v>
       </c>
@@ -2717,12 +2430,16 @@
       </c>
       <c r="V5" s="9"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="B6" s="9">
+        <v>5</v>
+      </c>
+      <c r="C6" s="15">
+        <v>25</v>
+      </c>
       <c r="D6" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="14">
         <v>98</v>
@@ -2779,12 +2496,16 @@
       <c r="AG6" s="19"/>
       <c r="AH6" s="19"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="B7" s="9">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9">
+        <v>25</v>
+      </c>
       <c r="D7" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14">
         <v>98</v>
@@ -2829,12 +2550,16 @@
       </c>
       <c r="V7" s="9"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="9">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9">
+        <v>25</v>
+      </c>
       <c r="D8" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="14">
         <v>98</v>
@@ -2879,12 +2604,16 @@
       </c>
       <c r="V8" s="9"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>25</v>
+      </c>
       <c r="D9" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="14">
         <v>98</v>
@@ -2929,12 +2658,16 @@
       </c>
       <c r="V9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="B10" s="9">
+        <v>9</v>
+      </c>
+      <c r="C10" s="9">
+        <v>25</v>
+      </c>
       <c r="D10" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="14">
         <v>98</v>
@@ -2979,12 +2712,16 @@
       </c>
       <c r="V10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="B11" s="9">
+        <v>10</v>
+      </c>
+      <c r="C11" s="9">
+        <v>15</v>
+      </c>
       <c r="D11" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="14">
         <v>76</v>
@@ -3031,12 +2768,16 @@
       </c>
       <c r="V11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="B12" s="9">
+        <v>11</v>
+      </c>
+      <c r="C12" s="9">
+        <v>15</v>
+      </c>
       <c r="D12" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="14">
         <v>76</v>
@@ -3083,12 +2824,16 @@
       </c>
       <c r="V12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="B13" s="9">
+        <v>12</v>
+      </c>
+      <c r="C13" s="9">
+        <v>15</v>
+      </c>
       <c r="D13" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="14">
         <v>76</v>
@@ -3135,12 +2880,16 @@
       </c>
       <c r="V13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="B14" s="9">
+        <v>13</v>
+      </c>
+      <c r="C14" s="9">
+        <v>15</v>
+      </c>
       <c r="D14" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="14">
         <v>83</v>
@@ -3185,12 +2934,16 @@
       </c>
       <c r="V14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="9">
+        <v>14</v>
+      </c>
+      <c r="C15" s="9">
+        <v>10</v>
+      </c>
       <c r="D15" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="14">
         <v>68</v>
@@ -3229,12 +2982,16 @@
       </c>
       <c r="V15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="B16" s="9">
+        <v>15</v>
+      </c>
+      <c r="C16" s="9">
+        <v>10</v>
+      </c>
       <c r="D16" s="9">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E16" s="14">
         <v>36</v>
@@ -3279,12 +3036,16 @@
       </c>
       <c r="V16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="9">
+        <v>16</v>
+      </c>
+      <c r="C17" s="9">
+        <v>11</v>
+      </c>
       <c r="D17" s="9">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E17" s="14">
         <v>30</v>
@@ -3329,12 +3090,16 @@
       </c>
       <c r="V17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="9">
+        <v>17</v>
+      </c>
+      <c r="C18" s="9">
+        <v>12</v>
+      </c>
       <c r="D18" s="9">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E18" s="14">
         <v>30</v>
@@ -3379,12 +3144,16 @@
       </c>
       <c r="V18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="9">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9">
+        <v>13</v>
+      </c>
       <c r="D19" s="9">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E19" s="14">
         <v>30</v>
@@ -3429,12 +3198,16 @@
       </c>
       <c r="V19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="9">
+        <v>19</v>
+      </c>
+      <c r="C20" s="9">
+        <v>11</v>
+      </c>
       <c r="D20" s="9">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="E20" s="14">
         <v>45</v>
@@ -3479,12 +3252,16 @@
       </c>
       <c r="V20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="9">
+        <v>20</v>
+      </c>
+      <c r="C21" s="9">
+        <v>10</v>
+      </c>
       <c r="D21" s="9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E21" s="14">
         <v>48</v>
@@ -3529,12 +3306,16 @@
       </c>
       <c r="V21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="9">
+        <v>21</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
       <c r="D22" s="9">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E22" s="14">
         <v>48</v>
@@ -3579,12 +3360,16 @@
       </c>
       <c r="V22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="9">
+        <v>22</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
       <c r="D23" s="9">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E23" s="14">
         <v>45</v>
@@ -3629,12 +3414,16 @@
       </c>
       <c r="V23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="9">
+        <v>23</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
       <c r="D24" s="9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
         <v>43</v>
@@ -3679,12 +3468,16 @@
       </c>
       <c r="V24" s="9"/>
     </row>
-    <row r="25" ht="23.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="9">
+        <v>24</v>
+      </c>
+      <c r="C25" s="9">
+        <v>12</v>
+      </c>
       <c r="D25" s="9">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
         <v>57</v>
@@ -3729,36 +3522,46 @@
       </c>
       <c r="V25" s="9"/>
     </row>
-    <row r="26" ht="16.5">
+    <row r="26" spans="1:22" ht="31.8" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="9">
+        <v>25</v>
+      </c>
+      <c r="C26" s="9">
+        <v>12</v>
+      </c>
       <c r="D26" s="9">
-        <v>50</v>
-      </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21">
-        <v>98</v>
-      </c>
-      <c r="H26" s="21"/>
-      <c r="I26" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J26" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="39">
+        <v>67</v>
+      </c>
+      <c r="F26" s="39">
+        <v>78</v>
+      </c>
+      <c r="G26" s="39">
         <v>85</v>
       </c>
+      <c r="H26" s="39">
+        <v>89</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="J26" s="41" t="s">
+        <v>215</v>
+      </c>
       <c r="K26" s="22" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O26" s="9"/>
+        <v>217</v>
+      </c>
+      <c r="O26" s="20"/>
       <c r="P26" s="9" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="Q26" s="13"/>
       <c r="R26" s="9"/>
@@ -3771,1847 +3574,521 @@
       </c>
       <c r="V26" s="9"/>
     </row>
-    <row r="27" ht="16.5">
+    <row r="27" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="9">
-        <v>51</v>
-      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="21">
-        <v>90</v>
-      </c>
+      <c r="G27" s="21"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
-      <c r="N27" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N27" s="9"/>
       <c r="O27" s="9"/>
-      <c r="P27" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="P27" s="9"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="9"/>
       <c r="S27" s="13"/>
-      <c r="T27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U27" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
       <c r="V27" s="9"/>
     </row>
-    <row r="28" ht="16.5">
+    <row r="28" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="9">
-        <v>52</v>
-      </c>
+      <c r="D28" s="9"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="21">
-        <v>95</v>
-      </c>
+      <c r="G28" s="21"/>
       <c r="H28" s="21"/>
-      <c r="I28" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N28" s="9"/>
       <c r="O28" s="9"/>
-      <c r="P28" s="9" t="s">
-        <v>90</v>
-      </c>
+      <c r="P28" s="9"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="9"/>
       <c r="S28" s="13"/>
-      <c r="T28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U28" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
       <c r="V28" s="9"/>
     </row>
-    <row r="29" ht="16.5">
+    <row r="29" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="9">
-        <v>53</v>
-      </c>
+      <c r="D29" s="9"/>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
-      <c r="G29" s="21">
-        <v>98</v>
-      </c>
+      <c r="G29" s="21"/>
       <c r="H29" s="21"/>
-      <c r="I29" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N29" s="9"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="9" t="s">
-        <v>91</v>
-      </c>
+      <c r="P29" s="9"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="9"/>
       <c r="S29" s="13"/>
-      <c r="T29" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
       <c r="V29" s="9"/>
     </row>
-    <row r="30" ht="16.5">
+    <row r="30" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="9">
-        <v>54</v>
-      </c>
+      <c r="D30" s="9"/>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
-      <c r="G30" s="21">
-        <v>98</v>
-      </c>
+      <c r="G30" s="21"/>
       <c r="H30" s="21"/>
-      <c r="I30" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N30" s="9"/>
       <c r="O30" s="9"/>
-      <c r="P30" s="9" t="s">
-        <v>92</v>
-      </c>
+      <c r="P30" s="9"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="9"/>
       <c r="S30" s="13"/>
-      <c r="T30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U30" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
       <c r="V30" s="9"/>
     </row>
-    <row r="31" ht="16.5">
+    <row r="31" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="9">
-        <v>55</v>
-      </c>
+      <c r="D31" s="9"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="21">
-        <v>98</v>
-      </c>
+      <c r="G31" s="21"/>
       <c r="H31" s="21"/>
-      <c r="I31" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N31" s="9"/>
       <c r="O31" s="9"/>
-      <c r="P31" s="9" t="s">
-        <v>93</v>
-      </c>
+      <c r="P31" s="9"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="9"/>
       <c r="S31" s="13"/>
-      <c r="T31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U31" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
       <c r="V31" s="9"/>
     </row>
-    <row r="32" ht="16.5">
+    <row r="32" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="9">
-        <v>56</v>
-      </c>
+      <c r="D32" s="9"/>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
-      <c r="G32" s="21">
-        <v>85</v>
-      </c>
+      <c r="G32" s="21"/>
       <c r="H32" s="21"/>
-      <c r="I32" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N32" s="9"/>
       <c r="O32" s="9"/>
-      <c r="P32" s="9" t="s">
-        <v>94</v>
-      </c>
+      <c r="P32" s="9"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="9"/>
       <c r="S32" s="13"/>
-      <c r="T32" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U32" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
       <c r="V32" s="9"/>
     </row>
-    <row r="33" ht="16.5">
+    <row r="33" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="9">
-        <v>57</v>
-      </c>
+      <c r="D33" s="9"/>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="21">
-        <v>85</v>
-      </c>
+      <c r="G33" s="21"/>
       <c r="H33" s="21"/>
-      <c r="I33" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J33" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K33" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
-      <c r="N33" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N33" s="9"/>
       <c r="O33" s="9"/>
-      <c r="P33" s="9" t="s">
-        <v>95</v>
-      </c>
+      <c r="P33" s="9"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="9"/>
       <c r="S33" s="13"/>
-      <c r="T33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U33" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
       <c r="V33" s="9"/>
     </row>
-    <row r="34" ht="16.5">
+    <row r="34" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="9">
-        <v>58</v>
-      </c>
+      <c r="D34" s="9"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
-      <c r="G34" s="21">
-        <v>85</v>
-      </c>
+      <c r="G34" s="21"/>
       <c r="H34" s="21"/>
-      <c r="I34" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N34" s="9"/>
       <c r="O34" s="9"/>
-      <c r="P34" s="9" t="s">
-        <v>96</v>
-      </c>
+      <c r="P34" s="9"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="9"/>
       <c r="S34" s="13"/>
-      <c r="T34" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U34" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
       <c r="V34" s="9"/>
     </row>
-    <row r="35" ht="16.5">
+    <row r="35" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="9">
-        <v>59</v>
-      </c>
+      <c r="D35" s="9"/>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
-      <c r="G35" s="21">
-        <v>75</v>
-      </c>
+      <c r="G35" s="21"/>
       <c r="H35" s="21"/>
-      <c r="I35" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K35" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N35" s="9"/>
       <c r="O35" s="9"/>
-      <c r="P35" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="P35" s="9"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="9"/>
       <c r="S35" s="13"/>
-      <c r="T35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U35" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
       <c r="V35" s="9"/>
     </row>
-    <row r="36" ht="16.5">
+    <row r="36" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="9">
-        <v>60</v>
-      </c>
+      <c r="D36" s="9"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
-      <c r="G36" s="21">
-        <v>75</v>
-      </c>
+      <c r="G36" s="21"/>
       <c r="H36" s="21"/>
-      <c r="I36" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J36" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K36" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N36" s="9"/>
       <c r="O36" s="9"/>
-      <c r="P36" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="P36" s="9"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="9"/>
       <c r="S36" s="13"/>
-      <c r="T36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U36" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
       <c r="V36" s="9"/>
     </row>
-    <row r="37" ht="16.5">
+    <row r="37" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="9">
-        <v>61</v>
-      </c>
+      <c r="D37" s="9"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="21">
-        <v>78</v>
-      </c>
+      <c r="G37" s="21"/>
       <c r="H37" s="21"/>
-      <c r="I37" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K37" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N37" s="9"/>
       <c r="O37" s="9"/>
-      <c r="P37" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="P37" s="9"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="9"/>
       <c r="S37" s="13"/>
-      <c r="T37" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U37" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
       <c r="V37" s="9"/>
     </row>
-    <row r="38" ht="16.5">
+    <row r="38" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="9">
-        <v>62</v>
-      </c>
+      <c r="D38" s="9"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
-      <c r="G38" s="21">
-        <v>81</v>
-      </c>
+      <c r="G38" s="21"/>
       <c r="H38" s="21"/>
-      <c r="I38" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J38" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K38" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
-      <c r="N38" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N38" s="9"/>
       <c r="O38" s="9"/>
-      <c r="P38" s="9" t="s">
-        <v>100</v>
-      </c>
+      <c r="P38" s="9"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="9"/>
       <c r="S38" s="13"/>
-      <c r="T38" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U38" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
       <c r="V38" s="9"/>
     </row>
-    <row r="39" ht="16.5">
+    <row r="39" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="9">
-        <v>63</v>
-      </c>
+      <c r="D39" s="9"/>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
-      <c r="G39" s="21">
-        <v>85</v>
-      </c>
+      <c r="G39" s="21"/>
       <c r="H39" s="21"/>
-      <c r="I39" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J39" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K39" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
-      <c r="N39" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N39" s="9"/>
       <c r="O39" s="9"/>
-      <c r="P39" s="9" t="s">
-        <v>101</v>
-      </c>
+      <c r="P39" s="9"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="9"/>
       <c r="S39" s="13"/>
-      <c r="T39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U39" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
       <c r="V39" s="9"/>
     </row>
-    <row r="40" ht="16.5">
+    <row r="40" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="9">
-        <v>64</v>
-      </c>
+      <c r="D40" s="9"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
-      <c r="G40" s="21">
-        <v>74</v>
-      </c>
+      <c r="G40" s="21"/>
       <c r="H40" s="21"/>
-      <c r="I40" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K40" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
-      <c r="N40" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N40" s="9"/>
       <c r="O40" s="9"/>
-      <c r="P40" s="9" t="s">
-        <v>102</v>
-      </c>
+      <c r="P40" s="9"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="9"/>
       <c r="S40" s="13"/>
-      <c r="T40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U40" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
       <c r="V40" s="9"/>
     </row>
-    <row r="41" ht="16.5">
+    <row r="41" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="9">
-        <v>65</v>
-      </c>
+      <c r="D41" s="9"/>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
-      <c r="G41" s="21">
-        <v>74</v>
-      </c>
+      <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J41" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
       <c r="L41" s="9"/>
       <c r="M41" s="9"/>
-      <c r="N41" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N41" s="9"/>
       <c r="O41" s="9"/>
-      <c r="P41" s="9" t="s">
-        <v>103</v>
-      </c>
+      <c r="P41" s="9"/>
       <c r="Q41" s="13"/>
       <c r="R41" s="9"/>
       <c r="S41" s="13"/>
-      <c r="T41" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U41" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
       <c r="V41" s="9"/>
     </row>
-    <row r="42" ht="16.5">
+    <row r="42" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="9">
-        <v>66</v>
-      </c>
+      <c r="D42" s="9"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
-      <c r="G42" s="21">
-        <v>74</v>
-      </c>
+      <c r="G42" s="21"/>
       <c r="H42" s="21"/>
-      <c r="I42" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J42" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I42" s="13"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
-      <c r="N42" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N42" s="9"/>
       <c r="O42" s="9"/>
-      <c r="P42" s="9" t="s">
-        <v>104</v>
-      </c>
+      <c r="P42" s="9"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="9"/>
       <c r="S42" s="13"/>
-      <c r="T42" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U42" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
       <c r="V42" s="9"/>
     </row>
-    <row r="43" ht="16.5">
+    <row r="43" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="9">
-        <v>67</v>
-      </c>
+      <c r="D43" s="9"/>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
-      <c r="G43" s="21">
-        <v>79</v>
-      </c>
+      <c r="G43" s="21"/>
       <c r="H43" s="21"/>
-      <c r="I43" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J43" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I43" s="13"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9"/>
-      <c r="N43" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N43" s="9"/>
       <c r="O43" s="9"/>
-      <c r="P43" s="9" t="s">
-        <v>105</v>
-      </c>
+      <c r="P43" s="9"/>
       <c r="Q43" s="13"/>
       <c r="R43" s="9"/>
       <c r="S43" s="13"/>
-      <c r="T43" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U43" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
       <c r="V43" s="9"/>
     </row>
-    <row r="44" ht="16.5">
+    <row r="44" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="9">
-        <v>68</v>
-      </c>
+      <c r="D44" s="9"/>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
-      <c r="G44" s="21">
-        <v>78</v>
-      </c>
+      <c r="G44" s="21"/>
       <c r="H44" s="21"/>
-      <c r="I44" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J44" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N44" s="9"/>
       <c r="O44" s="9"/>
-      <c r="P44" s="9" t="s">
-        <v>106</v>
-      </c>
+      <c r="P44" s="9"/>
       <c r="Q44" s="13"/>
       <c r="R44" s="9"/>
       <c r="S44" s="13"/>
-      <c r="T44" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U44" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
       <c r="V44" s="9"/>
     </row>
-    <row r="45" ht="16.5">
+    <row r="45" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="9">
-        <v>69</v>
-      </c>
+      <c r="D45" s="9"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
-      <c r="G45" s="21">
-        <v>78</v>
-      </c>
+      <c r="G45" s="21"/>
       <c r="H45" s="21"/>
-      <c r="I45" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J45" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N45" s="9"/>
       <c r="O45" s="9"/>
-      <c r="P45" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="P45" s="9"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="9"/>
       <c r="S45" s="13"/>
-      <c r="T45" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U45" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
       <c r="V45" s="9"/>
     </row>
-    <row r="46" ht="16.5">
+    <row r="46" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="9">
-        <v>70</v>
-      </c>
+      <c r="D46" s="9"/>
       <c r="E46" s="21"/>
       <c r="F46" s="21"/>
-      <c r="G46" s="21">
-        <v>78</v>
-      </c>
+      <c r="G46" s="21"/>
       <c r="H46" s="21"/>
-      <c r="I46" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J46" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K46" s="22" t="s">
-        <v>86</v>
-      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="N46" s="9"/>
       <c r="O46" s="9"/>
-      <c r="P46" s="9" t="s">
-        <v>108</v>
-      </c>
+      <c r="P46" s="9"/>
       <c r="Q46" s="13"/>
       <c r="R46" s="9"/>
       <c r="S46" s="13"/>
-      <c r="T46" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U46" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
       <c r="V46" s="9"/>
     </row>
-    <row r="47" ht="16.5">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9">
-        <v>71</v>
-      </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21">
-        <v>78</v>
-      </c>
-      <c r="H47" s="21"/>
-      <c r="I47" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J47" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K47" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V47" s="9"/>
-    </row>
-    <row r="48" ht="16.5">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9">
-        <v>72</v>
-      </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21">
-        <v>70</v>
-      </c>
-      <c r="H48" s="21"/>
-      <c r="I48" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J48" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K48" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U48" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V48" s="9"/>
-    </row>
-    <row r="49" ht="16.5">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9">
-        <v>73</v>
-      </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21">
-        <v>70</v>
-      </c>
-      <c r="H49" s="21"/>
-      <c r="I49" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J49" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K49" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V49" s="9"/>
-    </row>
-    <row r="50" ht="16.5">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9">
-        <v>74</v>
-      </c>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21">
-        <v>70</v>
-      </c>
-      <c r="H50" s="21"/>
-      <c r="I50" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K50" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="13"/>
-      <c r="T50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U50" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V50" s="9"/>
-    </row>
-    <row r="51" ht="16.5">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9">
-        <v>75</v>
-      </c>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21">
-        <v>79</v>
-      </c>
-      <c r="H51" s="21"/>
-      <c r="I51" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J51" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K51" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V51" s="9"/>
-    </row>
-    <row r="52" ht="16.5">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9">
-        <v>76</v>
-      </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21">
-        <v>79</v>
-      </c>
-      <c r="H52" s="21"/>
-      <c r="I52" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J52" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K52" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q52" s="13"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U52" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V52" s="9"/>
-    </row>
-    <row r="53" ht="16.5">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9">
-        <v>77</v>
-      </c>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21">
-        <v>79</v>
-      </c>
-      <c r="H53" s="21"/>
-      <c r="I53" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J53" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K53" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q53" s="13"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V53" s="9"/>
-    </row>
-    <row r="54" ht="16.5">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9">
-        <v>78</v>
-      </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21">
-        <v>79</v>
-      </c>
-      <c r="H54" s="21"/>
-      <c r="I54" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J54" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K54" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q54" s="13"/>
-      <c r="R54" s="9"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U54" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V54" s="9"/>
-    </row>
-    <row r="55" ht="16.5">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9">
-        <v>79</v>
-      </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21">
-        <v>85</v>
-      </c>
-      <c r="H55" s="21"/>
-      <c r="I55" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J55" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K55" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q55" s="13"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V55" s="9"/>
-    </row>
-    <row r="56" ht="16.5">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9">
-        <v>80</v>
-      </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21">
-        <v>85</v>
-      </c>
-      <c r="H56" s="21"/>
-      <c r="I56" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J56" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K56" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q56" s="13"/>
-      <c r="R56" s="9"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U56" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V56" s="9"/>
-    </row>
-    <row r="57" ht="16.5">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9">
-        <v>81</v>
-      </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21">
-        <v>85</v>
-      </c>
-      <c r="H57" s="21"/>
-      <c r="I57" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K57" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q57" s="13"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V57" s="9"/>
-    </row>
-    <row r="58" ht="16.5">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9">
-        <v>82</v>
-      </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21">
-        <v>85</v>
-      </c>
-      <c r="H58" s="21"/>
-      <c r="I58" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K58" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q58" s="13"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U58" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V58" s="9"/>
-    </row>
-    <row r="59" ht="16.5">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9">
-        <v>83</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21">
-        <v>100</v>
-      </c>
-      <c r="H59" s="21"/>
-      <c r="I59" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J59" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K59" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q59" s="13"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V59" s="9"/>
-    </row>
-    <row r="60" ht="16.5">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9">
-        <v>84</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21">
-        <v>98</v>
-      </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J60" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K60" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q60" s="13"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U60" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V60" s="9"/>
-    </row>
-    <row r="61" ht="16.5">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9">
-        <v>85</v>
-      </c>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21">
-        <v>98</v>
-      </c>
-      <c r="H61" s="21"/>
-      <c r="I61" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J61" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K61" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="13"/>
-      <c r="T61" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V61" s="9"/>
-    </row>
-    <row r="62" ht="16.5">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9">
-        <v>86</v>
-      </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21">
-        <v>98</v>
-      </c>
-      <c r="H62" s="21"/>
-      <c r="I62" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J62" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K62" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="9"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U62" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V62" s="9"/>
-    </row>
-    <row r="63" ht="16.5">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9">
-        <v>87</v>
-      </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21">
-        <v>98</v>
-      </c>
-      <c r="H63" s="21"/>
-      <c r="I63" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J63" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K63" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O63" s="9"/>
-      <c r="P63" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q63" s="13"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V63" s="9"/>
-    </row>
-    <row r="64" ht="16.5">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9">
-        <v>88</v>
-      </c>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21">
-        <v>98</v>
-      </c>
-      <c r="H64" s="21"/>
-      <c r="I64" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J64" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K64" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q64" s="13"/>
-      <c r="R64" s="9"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U64" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V64" s="9"/>
-    </row>
-    <row r="65" ht="15.75">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9">
-        <v>89</v>
-      </c>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21">
-        <v>100</v>
-      </c>
-      <c r="H65" s="21"/>
-      <c r="I65" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J65" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K65" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L65" s="9"/>
-      <c r="M65" s="9"/>
-      <c r="N65" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O65" s="9"/>
-      <c r="P65" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q65" s="13"/>
-      <c r="R65" s="9"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V65" s="9"/>
-    </row>
-    <row r="66" ht="15.75">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9">
-        <v>90</v>
-      </c>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21">
-        <v>100</v>
-      </c>
-      <c r="H66" s="21"/>
-      <c r="I66" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J66" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K66" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L66" s="9"/>
-      <c r="M66" s="9"/>
-      <c r="N66" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q66" s="13"/>
-      <c r="R66" s="9"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U66" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V66" s="9"/>
-    </row>
-    <row r="67" ht="15.75">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9">
-        <v>91</v>
-      </c>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21">
-        <v>100</v>
-      </c>
-      <c r="H67" s="21"/>
-      <c r="I67" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J67" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L67" s="9"/>
-      <c r="M67" s="9"/>
-      <c r="N67" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O67" s="9"/>
-      <c r="P67" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q67" s="13"/>
-      <c r="R67" s="9"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V67" s="9"/>
-    </row>
-    <row r="68" ht="15.75">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9">
-        <v>92</v>
-      </c>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21">
-        <v>100</v>
-      </c>
-      <c r="H68" s="21"/>
-      <c r="I68" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J68" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K68" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9"/>
-      <c r="N68" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q68" s="13"/>
-      <c r="R68" s="9"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U68" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V68" s="9"/>
-    </row>
-    <row r="69" ht="15.75">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9">
-        <v>93</v>
-      </c>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21">
-        <v>100</v>
-      </c>
-      <c r="H69" s="21"/>
-      <c r="I69" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J69" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K69" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L69" s="9"/>
-      <c r="M69" s="9"/>
-      <c r="N69" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O69" s="9"/>
-      <c r="P69" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q69" s="13"/>
-      <c r="R69" s="9"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="U69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V69" s="9"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
-  <printOptions headings="0" gridLines="0"/>
+  <autoFilter ref="A1:V15" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.42578125"/>
-    <col customWidth="1" min="2" max="2" width="8.28515625"/>
-    <col customWidth="1" min="3" max="3" width="16.28515625"/>
-    <col customWidth="1" min="4" max="4" width="4.28515625"/>
-    <col customWidth="1" min="5" max="5" width="63.140625"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="B2" s="9">
         <v>5</v>
@@ -5622,9 +4099,9 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="B3" s="9">
         <v>50</v>
@@ -5633,15 +4110,15 @@
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="B4" s="9">
         <v>50</v>
@@ -5650,26 +4127,26 @@
         <v>90</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="B6" s="9">
         <v>30</v>
@@ -5679,12 +4156,12 @@
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="B7" s="9">
         <v>10</v>
@@ -5693,15 +4170,15 @@
         <v>40</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="B8" s="9">
         <v>15</v>
@@ -5711,21 +4188,21 @@
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="B10" s="9">
         <v>15</v>
@@ -5736,9 +4213,9 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="B11" s="9">
         <v>15</v>
@@ -5749,17 +4226,17 @@
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="B12" s="23">
         <v>50</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="B13">
         <v>15</v>
@@ -5768,27 +4245,78 @@
         <v>50</v>
       </c>
     </row>
+    <row r="24" spans="1:22" s="1" customFormat="1" ht="31.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9">
+        <v>25</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="9">
+        <v>25</v>
+      </c>
+      <c r="E24" s="39">
+        <v>67</v>
+      </c>
+      <c r="F24" s="39">
+        <v>78</v>
+      </c>
+      <c r="G24" s="39">
+        <v>85</v>
+      </c>
+      <c r="H24" s="39">
+        <v>89</v>
+      </c>
+      <c r="I24" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="J24" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="O24" s="20"/>
+      <c r="P24" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="U24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="9"/>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.85546875"/>
-    <col customWidth="1" min="2" max="6" width="4"/>
-    <col customWidth="1" min="7" max="11" width="3"/>
-    <col customWidth="1" min="12" max="12" width="4"/>
+    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="2" max="6" width="4" customWidth="1"/>
+    <col min="7" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="B1" s="9">
         <v>50</v>
@@ -5824,9 +4352,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="B2" s="24">
         <f t="shared" ref="B2:L2" si="0">254*(100/B1-1)</f>
@@ -5874,277 +4402,274 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.42578125"/>
-    <col customWidth="1" min="2" max="2" width="53.140625"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.5703125"/>
-    <col customWidth="1" min="2" max="2" width="127.140625"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="127.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="114">
+    <row r="1" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B8"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="28.140625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="34.5703125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="19.28515625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="19.140625"/>
-    <col bestFit="1" customWidth="1" min="5" max="6" width="19.28515625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="9.28515625"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1">
+    <row r="1" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" ht="15">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="29">
         <v>111</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="C2" s="29">
         <v>98</v>
@@ -6162,16 +4687,16 @@
         <v>111</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H9" si="1">"LIKE '%"&amp;G2&amp;"%'"</f>
-        <v xml:space="preserve">LIKE '%111%'</v>
-      </c>
-    </row>
-    <row r="3" ht="15">
+        <f t="shared" ref="H2:H9" si="0">"LIKE '%"&amp;G2&amp;"%'"</f>
+        <v>LIKE '%111%'</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>112</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="C3" s="29">
         <v>90</v>
@@ -6189,16 +4714,16 @@
         <v>112</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%112%'</v>
-      </c>
-    </row>
-    <row r="4" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%112%'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <v>121</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="C4" s="29">
         <v>95</v>
@@ -6216,16 +4741,16 @@
         <v>121</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%121%'</v>
-      </c>
-    </row>
-    <row r="5" ht="30">
+        <f t="shared" si="0"/>
+        <v>LIKE '%121%'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>122</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="C5" s="29">
         <v>98</v>
@@ -6243,16 +4768,16 @@
         <v>122</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%122%'</v>
-      </c>
-    </row>
-    <row r="6" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%122%'</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <v>123</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="C6" s="29">
         <v>98</v>
@@ -6270,16 +4795,16 @@
         <v>123</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%123%'</v>
-      </c>
-    </row>
-    <row r="7" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%123%'</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <v>124</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="C7" s="29">
         <v>98</v>
@@ -6297,16 +4822,16 @@
         <v>124</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%124%'</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%124%'</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <v>131</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="C8" s="29">
         <v>85</v>
@@ -6324,16 +4849,16 @@
         <v>131</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%131%'</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%131%'</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <v>132</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="C9" s="29">
         <v>85</v>
@@ -6351,16 +4876,16 @@
         <v>132</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">LIKE '%132%'</v>
-      </c>
-    </row>
-    <row r="10" ht="15">
+        <f t="shared" si="0"/>
+        <v>LIKE '%132%'</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <v>133</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="C10" s="29">
         <v>85</v>
@@ -6378,16 +4903,16 @@
         <v>133</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" ref="H10:H45" si="2">"LIKE '%"&amp;G10&amp;"%'"</f>
-        <v xml:space="preserve">LIKE '%133%'</v>
-      </c>
-    </row>
-    <row r="11" ht="15">
+        <f t="shared" ref="H10:H45" si="1">"LIKE '%"&amp;G10&amp;"%'"</f>
+        <v>LIKE '%133%'</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <v>141</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="C11" s="29">
         <v>61</v>
@@ -6405,16 +4930,16 @@
         <v>141</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%141%'</v>
-      </c>
-    </row>
-    <row r="12" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%141%'</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <v>142</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="C12" s="29">
         <v>61</v>
@@ -6432,16 +4957,16 @@
         <v>142</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%142%'</v>
-      </c>
-    </row>
-    <row r="13" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%142%'</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <v>211</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="C13" s="29">
         <v>67</v>
@@ -6459,16 +4984,16 @@
         <v>211</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%211%'</v>
-      </c>
-    </row>
-    <row r="14" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%211%'</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>212</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="C14" s="29">
         <v>72</v>
@@ -6486,16 +5011,16 @@
         <v>212</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%212%'</v>
-      </c>
-    </row>
-    <row r="15" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%212%'</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <v>213</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
       <c r="C15" s="29">
         <v>77</v>
@@ -6513,16 +5038,16 @@
         <v>213</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%213%'</v>
-      </c>
-    </row>
-    <row r="16" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%213%'</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <v>221</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
       <c r="C16" s="29">
         <v>63</v>
@@ -6540,16 +5065,16 @@
         <v>221</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%221%'</v>
-      </c>
-    </row>
-    <row r="17" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%221%'</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <v>222</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="C17" s="29">
         <v>63</v>
@@ -6567,16 +5092,16 @@
         <v>222</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%222%'</v>
-      </c>
-    </row>
-    <row r="18" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%222%'</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="29">
         <v>223</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="C18" s="29">
         <v>63</v>
@@ -6594,16 +5119,16 @@
         <v>223</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%223%'</v>
-      </c>
-    </row>
-    <row r="19" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%223%'</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="29">
         <v>231</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="C19" s="29">
         <v>68</v>
@@ -6621,16 +5146,16 @@
         <v>231</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%231%'</v>
-      </c>
-    </row>
-    <row r="20" ht="30">
+        <f t="shared" si="1"/>
+        <v>LIKE '%231%'</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <v>241</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="C20" s="29">
         <v>67</v>
@@ -6648,16 +5173,16 @@
         <v>241</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%241%'</v>
-      </c>
-    </row>
-    <row r="21" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%241%'</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="29">
         <v>242</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="C21" s="29">
         <v>67</v>
@@ -6675,16 +5200,16 @@
         <v>242</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%242%'</v>
-      </c>
-    </row>
-    <row r="22" ht="45">
+        <f t="shared" si="1"/>
+        <v>LIKE '%242%'</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <v>243</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="C22" s="29">
         <v>67</v>
@@ -6702,16 +5227,16 @@
         <v>243</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%243%'</v>
-      </c>
-    </row>
-    <row r="23" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%243%'</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
         <v>244</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="C23" s="29">
         <v>67</v>
@@ -6729,16 +5254,16 @@
         <v>244</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%244%'</v>
-      </c>
-    </row>
-    <row r="24" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%244%'</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="29">
         <v>311</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="C24" s="29">
         <v>55</v>
@@ -6756,16 +5281,16 @@
         <v>311</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%311%'</v>
-      </c>
-    </row>
-    <row r="25" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%311%'</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <v>312</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="C25" s="29">
         <v>55</v>
@@ -6783,16 +5308,16 @@
         <v>312</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%312%'</v>
-      </c>
-    </row>
-    <row r="26" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%312%'</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="29">
         <v>313</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="C26" s="29">
         <v>55</v>
@@ -6810,16 +5335,16 @@
         <v>313</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%313%'</v>
-      </c>
-    </row>
-    <row r="27" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%313%'</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="29">
         <v>321</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="C27" s="29">
         <v>68</v>
@@ -6837,16 +5362,16 @@
         <v>321</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%321%'</v>
-      </c>
-    </row>
-    <row r="28" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%321%'</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <v>322</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="C28" s="29">
         <v>68</v>
@@ -6864,16 +5389,16 @@
         <v>322</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%322%'</v>
-      </c>
-    </row>
-    <row r="29" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%322%'</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="29">
         <v>323</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="C29" s="29">
         <v>68</v>
@@ -6891,16 +5416,16 @@
         <v>323</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%323%'</v>
-      </c>
-    </row>
-    <row r="30" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%323%'</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
         <v>324</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="C30" s="29">
         <v>68</v>
@@ -6918,16 +5443,16 @@
         <v>324</v>
       </c>
       <c r="H30" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%324%'</v>
-      </c>
-    </row>
-    <row r="31" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%324%'</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <v>331</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="C31" s="29">
         <v>77</v>
@@ -6945,16 +5470,16 @@
         <v>331</v>
       </c>
       <c r="H31" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%331%'</v>
-      </c>
-    </row>
-    <row r="32" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%331%'</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="29">
         <v>332</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="C32" s="29">
         <v>77</v>
@@ -6972,16 +5497,16 @@
         <v>332</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%332%'</v>
-      </c>
-    </row>
-    <row r="33" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%332%'</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="29">
         <v>333</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="C33" s="29">
         <v>77</v>
@@ -6999,16 +5524,16 @@
         <v>333</v>
       </c>
       <c r="H33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%333%'</v>
-      </c>
-    </row>
-    <row r="34" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%333%'</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <v>334</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="C34" s="29">
         <v>77</v>
@@ -7026,16 +5551,16 @@
         <v>334</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%334%'</v>
-      </c>
-    </row>
-    <row r="35" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%334%'</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <v>335</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="C35" s="29">
         <v>100</v>
@@ -7053,16 +5578,16 @@
         <v>335</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%335%'</v>
-      </c>
-    </row>
-    <row r="36" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%335%'</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="29">
         <v>411</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C36" s="29">
         <v>98</v>
@@ -7080,16 +5605,16 @@
         <v>411</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%411%'</v>
-      </c>
-    </row>
-    <row r="37" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%411%'</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
         <v>412</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="C37" s="29">
         <v>98</v>
@@ -7107,16 +5632,16 @@
         <v>412</v>
       </c>
       <c r="H37" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%412%'</v>
-      </c>
-    </row>
-    <row r="38" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%412%'</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
         <v>421</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C38" s="29">
         <v>98</v>
@@ -7134,16 +5659,16 @@
         <v>421</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%421%'</v>
-      </c>
-    </row>
-    <row r="39" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%421%'</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
         <v>422</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="C39" s="29">
         <v>98</v>
@@ -7161,16 +5686,16 @@
         <v>422</v>
       </c>
       <c r="H39" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%422%'</v>
-      </c>
-    </row>
-    <row r="40" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%422%'</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
         <v>423</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="C40" s="29">
         <v>98</v>
@@ -7188,16 +5713,16 @@
         <v>423</v>
       </c>
       <c r="H40" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%423%'</v>
-      </c>
-    </row>
-    <row r="41" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%423%'</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
         <v>511</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="C41" s="29">
         <v>100</v>
@@ -7215,16 +5740,16 @@
         <v>511</v>
       </c>
       <c r="H41" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%511%'</v>
-      </c>
-    </row>
-    <row r="42" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%511%'</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="29">
         <v>512</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="C42" s="29">
         <v>100</v>
@@ -7242,16 +5767,16 @@
         <v>512</v>
       </c>
       <c r="H42" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%512%'</v>
-      </c>
-    </row>
-    <row r="43" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%512%'</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="29">
         <v>521</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="C43" s="29">
         <v>100</v>
@@ -7269,16 +5794,16 @@
         <v>521</v>
       </c>
       <c r="H43" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%521%'</v>
-      </c>
-    </row>
-    <row r="44" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%521%'</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="29">
         <v>522</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="C44" s="29">
         <v>100</v>
@@ -7296,16 +5821,16 @@
         <v>522</v>
       </c>
       <c r="H44" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%522%'</v>
-      </c>
-    </row>
-    <row r="45" ht="15">
+        <f t="shared" si="1"/>
+        <v>LIKE '%522%'</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="29">
         <v>523</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="C45" s="29">
         <v>100</v>
@@ -7323,102 +5848,101 @@
         <v>523</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">LIKE '%523%'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '%523%'</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" style="30" width="31.28515625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" style="30" width="34.42578125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="30" width="2"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" style="30" width="18.42578125"/>
-    <col min="5" max="7" style="30" width="11.42578125"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" style="30" width="22.28515625"/>
-    <col customWidth="1" min="9" max="10" style="30" width="22.28515625"/>
-    <col min="11" max="16384" style="30" width="11.42578125"/>
+    <col min="1" max="1" width="31.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.44140625" style="30"/>
+    <col min="8" max="8" width="22.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.33203125" style="30" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D1" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
-      <c r="K1" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2">
+      <c r="K1" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="J2" s="32"/>
       <c r="K2" s="30" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="O2" s="30" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" ht="28.5">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
         <v>1</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="C3" s="30">
-        <f t="shared" ref="C3:C26" si="3">IF(A2=A3,0,1)</f>
+        <f t="shared" ref="C3:C26" si="0">IF(A2=A3,0,1)</f>
         <v>1</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E3" s="34">
         <v>67</v>
@@ -7436,8 +5960,8 @@
         <v>1</v>
       </c>
       <c r="J3" s="1" t="str">
-        <f t="shared" ref="J3:J30" si="4">"LIKE '"&amp;I3&amp;"'"</f>
-        <v xml:space="preserve">LIKE '1'</v>
+        <f t="shared" ref="J3:J30" si="1">"LIKE '"&amp;I3&amp;"'"</f>
+        <v>LIKE '1'</v>
       </c>
       <c r="K3" s="30">
         <v>1</v>
@@ -7455,19 +5979,19 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" ht="28.5">
+    <row r="4" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
         <v>2</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="C4" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E4" s="34">
         <v>67</v>
@@ -7485,8 +6009,8 @@
         <v>2</v>
       </c>
       <c r="J4" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '2'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '2'</v>
       </c>
       <c r="K4" s="30">
         <v>2</v>
@@ -7504,19 +6028,19 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" ht="28.5">
+    <row r="5" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="32">
         <v>3</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="C5" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E5" s="34">
         <v>67</v>
@@ -7534,8 +6058,8 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '3'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '3'</v>
       </c>
       <c r="K5" s="30">
         <v>3</v>
@@ -7553,19 +6077,19 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" ht="28.5">
+    <row r="6" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
         <v>4</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="C6" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E6" s="34">
         <v>67</v>
@@ -7583,8 +6107,8 @@
         <v>4</v>
       </c>
       <c r="J6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '4'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '4'</v>
       </c>
       <c r="K6" s="30">
         <v>4</v>
@@ -7602,19 +6126,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" ht="28.5">
+    <row r="7" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="32">
         <v>5</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="C7" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E7" s="34">
         <v>67</v>
@@ -7632,8 +6156,8 @@
         <v>5</v>
       </c>
       <c r="J7" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '5'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '5'</v>
       </c>
       <c r="K7" s="30">
         <v>5</v>
@@ -7651,19 +6175,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" ht="28.5">
+    <row r="8" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="32">
         <v>6</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="C8" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E8" s="34">
         <v>67</v>
@@ -7681,8 +6205,8 @@
         <v>6</v>
       </c>
       <c r="J8" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '6'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '6'</v>
       </c>
       <c r="K8" s="30">
         <v>6</v>
@@ -7700,19 +6224,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" ht="28.5">
+    <row r="9" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="32">
         <v>7</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="C9" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E9" s="34">
         <v>67</v>
@@ -7730,8 +6254,8 @@
         <v>7</v>
       </c>
       <c r="J9" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '7'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '7'</v>
       </c>
       <c r="K9" s="30">
         <v>7</v>
@@ -7749,19 +6273,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" ht="28.5">
+    <row r="10" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="32">
         <v>8</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="C10" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E10" s="34">
         <v>67</v>
@@ -7779,8 +6303,8 @@
         <v>8</v>
       </c>
       <c r="J10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '8'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '8'</v>
       </c>
       <c r="K10" s="30">
         <v>8</v>
@@ -7798,19 +6322,19 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" ht="28.5">
+    <row r="11" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="32">
         <v>9</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="C11" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E11" s="34">
         <v>67</v>
@@ -7828,8 +6352,8 @@
         <v>9</v>
       </c>
       <c r="J11" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '9'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '9'</v>
       </c>
       <c r="K11" s="30">
         <v>9</v>
@@ -7847,15 +6371,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" ht="15">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="32">
         <v>11</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="C12" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E12" s="32">
@@ -7874,8 +6398,8 @@
         <v>11</v>
       </c>
       <c r="J12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '11'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '11'</v>
       </c>
       <c r="K12" s="30">
         <v>10</v>
@@ -7893,19 +6417,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" ht="28.5">
+    <row r="13" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="32">
         <v>14</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="C13" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E13" s="34">
         <v>77</v>
@@ -7923,8 +6447,8 @@
         <v>14</v>
       </c>
       <c r="J13" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '14'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '14'</v>
       </c>
       <c r="K13" s="30">
         <v>11</v>
@@ -7942,19 +6466,19 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" ht="28.5">
+    <row r="14" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="32">
         <v>15</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="C14" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E14" s="34">
         <v>67</v>
@@ -7972,8 +6496,8 @@
         <v>15</v>
       </c>
       <c r="J14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '15'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '15'</v>
       </c>
       <c r="K14" s="30">
         <v>12</v>
@@ -7991,19 +6515,19 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" ht="28.5">
+    <row r="15" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="32">
         <v>16</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="C15" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E15" s="34">
         <v>68</v>
@@ -8021,8 +6545,8 @@
         <v>16</v>
       </c>
       <c r="J15" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '16'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '16'</v>
       </c>
       <c r="K15" s="30">
         <v>13</v>
@@ -8040,19 +6564,19 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" ht="28.5">
+    <row r="16" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="32">
         <v>17</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="C16" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E16" s="34">
         <v>30</v>
@@ -8070,8 +6594,8 @@
         <v>17</v>
       </c>
       <c r="J16" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '17'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '17'</v>
       </c>
       <c r="K16" s="30">
         <v>14</v>
@@ -8089,19 +6613,19 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" ht="28.5">
+    <row r="17" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A17" s="32">
         <v>18</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="C17" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E17" s="35">
         <v>49</v>
@@ -8119,8 +6643,8 @@
         <v>18</v>
       </c>
       <c r="J17" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '18'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '18'</v>
       </c>
       <c r="K17" s="30">
         <v>15</v>
@@ -8138,19 +6662,19 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" ht="28.5">
+    <row r="18" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="32">
         <v>19</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="C18" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E18" s="34">
         <v>68</v>
@@ -8168,8 +6692,8 @@
         <v>19</v>
       </c>
       <c r="J18" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '19'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '19'</v>
       </c>
       <c r="K18" s="30">
         <v>16</v>
@@ -8187,19 +6711,19 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" ht="28.5">
+    <row r="19" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="32">
         <v>20</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="C19" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E19" s="36">
         <v>43</v>
@@ -8217,8 +6741,8 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '20'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '20'</v>
       </c>
       <c r="K19" s="30">
         <v>17</v>
@@ -8236,19 +6760,19 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" ht="28.5">
+    <row r="20" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="32">
         <v>21</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="C20" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E20" s="36">
         <v>57</v>
@@ -8266,8 +6790,8 @@
         <v>21</v>
       </c>
       <c r="J20" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '21'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '21'</v>
       </c>
       <c r="K20" s="30">
         <v>18</v>
@@ -8285,19 +6809,19 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" ht="28.5">
+    <row r="21" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="32">
         <v>22</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="C21" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E21" s="34">
         <v>63</v>
@@ -8315,8 +6839,8 @@
         <v>22</v>
       </c>
       <c r="J21" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '22'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '22'</v>
       </c>
       <c r="K21" s="30">
         <v>19</v>
@@ -8334,19 +6858,19 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" ht="28.5">
+    <row r="22" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="32">
         <v>23</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="C22" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E22" s="36">
         <v>43</v>
@@ -8364,8 +6888,8 @@
         <v>23</v>
       </c>
       <c r="J22" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '23'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '23'</v>
       </c>
       <c r="K22" s="30">
         <v>20</v>
@@ -8383,15 +6907,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" ht="15">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="32">
         <v>24</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="C23" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E23" s="34">
@@ -8410,8 +6934,8 @@
         <v>24</v>
       </c>
       <c r="J23" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '24'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '24'</v>
       </c>
       <c r="K23" s="30">
         <v>21</v>
@@ -8429,19 +6953,19 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" ht="28.5">
+    <row r="24" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="32">
         <v>25</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="C24" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E24" s="34">
         <v>67</v>
@@ -8459,8 +6983,8 @@
         <v>25</v>
       </c>
       <c r="J24" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '25'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '25'</v>
       </c>
       <c r="K24" s="30">
         <v>22</v>
@@ -8478,19 +7002,19 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" ht="28.5">
+    <row r="25" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="32">
         <v>26</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="C25" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E25" s="34">
         <v>67</v>
@@ -8508,8 +7032,8 @@
         <v>26</v>
       </c>
       <c r="J25" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '26'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '26'</v>
       </c>
       <c r="K25" s="30">
         <v>23</v>
@@ -8527,15 +7051,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" ht="15">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="32">
         <v>28</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="C26" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E26" s="34">
@@ -8554,8 +7078,8 @@
         <v>28</v>
       </c>
       <c r="J26" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE '28'</v>
+        <f t="shared" si="1"/>
+        <v>LIKE '28'</v>
       </c>
       <c r="K26" s="30">
         <v>24</v>
@@ -8573,10 +7097,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" ht="15">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J27" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE ''</v>
+        <f t="shared" si="1"/>
+        <v>LIKE ''</v>
       </c>
       <c r="K27" s="30">
         <v>25</v>
@@ -8594,10 +7118,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" ht="15">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J28" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE ''</v>
+        <f t="shared" si="1"/>
+        <v>LIKE ''</v>
       </c>
       <c r="K28" s="30">
         <v>26</v>
@@ -8615,10 +7139,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" ht="15">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J29" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE ''</v>
+        <f t="shared" si="1"/>
+        <v>LIKE ''</v>
       </c>
       <c r="K29" s="30">
         <v>27</v>
@@ -8636,10 +7160,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" ht="15">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J30" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">LIKE ''</v>
+        <f t="shared" si="1"/>
+        <v>LIKE ''</v>
       </c>
       <c r="K30" s="30">
         <v>28</v>
@@ -8658,14 +7182,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C26"/>
+  <autoFilter ref="A2:C26" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <mergeCells count="2">
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="K1:O1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>